--- a/data/Car_Maintainance_Schedule.xlsx
+++ b/data/Car_Maintainance_Schedule.xlsx
@@ -398,7 +398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -1710,6 +1710,49 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Anish</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Anish</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ANish</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ANish</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Gopal</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Gopal</t>
+        </is>
+      </c>
+    </row>
+    <row r="67"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
